--- a/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Nonlinear.xlsx
+++ b/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Nonlinear.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Springs\Spring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3FCFDD-12EF-4428-AAC3-668FF87CE2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E18E21-8B54-44F8-8CB0-9C07CC971E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{4B72BAB0-EF5A-47BE-A61B-4D620C6D1400}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{4B72BAB0-EF5A-47BE-A61B-4D620C6D1400}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_HambaLG_f" sheetId="1" r:id="rId1"/>
     <sheet name="Sedan_HambaLG_r" sheetId="2" r:id="rId2"/>
     <sheet name="SUV_Landy_TA4Watts_r" sheetId="3" r:id="rId3"/>
+    <sheet name="SUV_Landy_TA3_r" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="23">
   <si>
     <t>Units</t>
   </si>
@@ -76,9 +77,6 @@
     <t>sBottom</t>
   </si>
   <si>
-    <t>xPreload</t>
-  </si>
-  <si>
     <t>xSpring</t>
   </si>
   <si>
@@ -103,10 +101,10 @@
     <t>fPreload</t>
   </si>
   <si>
-    <t>Set either xPreload or fPreload to a nonzero value</t>
-  </si>
-  <si>
     <t>SUV_Landy_TA4Watts_Nonlinear_A2</t>
+  </si>
+  <si>
+    <t>SUV_Landy_TA3_Nonlinear_A2</t>
   </si>
 </sst>
 </file>
@@ -187,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -233,11 +231,26 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -628,326 +641,6 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.42578125" style="15" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="8" width="10" customWidth="1"/>
-    <col min="9" max="14" width="6.7109375" customWidth="1"/>
-    <col min="15" max="15" width="7" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="21">
-        <v>-2.6557142857142869E-3</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0.62</v>
-      </c>
-      <c r="H5" s="22">
-        <v>0.65</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="21">
-        <v>5.5166428571428582E-2</v>
-      </c>
-      <c r="G6" s="22">
-        <v>0.85</v>
-      </c>
-      <c r="H6" s="22">
-        <v>0.19</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="6">
-        <v>-1</v>
-      </c>
-      <c r="I9" s="13">
-        <v>-0.5</v>
-      </c>
-      <c r="J9" s="13">
-        <v>-0.3</v>
-      </c>
-      <c r="K9" s="13">
-        <v>-0.1</v>
-      </c>
-      <c r="L9" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="M9" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="N9" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="O9" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="14">
-        <f t="shared" ref="H10:O10" si="0">H9*$L$12</f>
-        <v>-140000</v>
-      </c>
-      <c r="I10" s="14">
-        <f t="shared" si="0"/>
-        <v>-70000</v>
-      </c>
-      <c r="J10" s="14">
-        <f t="shared" si="0"/>
-        <v>-42000</v>
-      </c>
-      <c r="K10" s="14">
-        <f t="shared" si="0"/>
-        <v>-14000</v>
-      </c>
-      <c r="L10" s="14">
-        <f t="shared" si="0"/>
-        <v>14000</v>
-      </c>
-      <c r="M10" s="14">
-        <f t="shared" si="0"/>
-        <v>42000</v>
-      </c>
-      <c r="N10" s="14">
-        <f t="shared" si="0"/>
-        <v>70000</v>
-      </c>
-      <c r="O10" s="14">
-        <f t="shared" si="0"/>
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="J12" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="17">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="18"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="15"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B15" s="15"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="15"/>
-      <c r="H18" s="19"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="15"/>
-      <c r="H19" s="19"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A4:A10">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14:B17">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E476D5-D5F4-46B8-B8AE-896516844BE5}">
-  <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
-  </sheetPr>
   <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1003,7 +696,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -1030,10 +723,10 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="21">
-        <v>2.6557142857142869E-3</v>
+        <v>-2.6557142857142869E-3</v>
       </c>
       <c r="G5" s="22">
         <v>0.62</v>
@@ -1042,7 +735,7 @@
         <v>0.65</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -1055,10 +748,10 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" s="21">
-        <v>-5.5166428571428582E-2</v>
+        <v>5.5166428571428582E-2</v>
       </c>
       <c r="G6" s="22">
         <v>0.85</v>
@@ -1067,41 +760,58 @@
         <v>0.19</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>22</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="E7" s="12"/>
       <c r="G7" s="12"/>
       <c r="H7" s="6">
-        <v>0.06</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>22</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F8" s="12"/>
       <c r="G8" s="12"/>
       <c r="H8" s="6">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="I8" s="13">
+        <v>-0.5</v>
+      </c>
+      <c r="J8" s="13">
+        <v>-0.3</v>
+      </c>
+      <c r="K8" s="13">
+        <v>-0.1</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="N8" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="O8" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -1111,95 +821,67 @@
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
-      <c r="H9" s="6">
-        <v>-1</v>
-      </c>
-      <c r="I9" s="6">
-        <v>-0.5</v>
-      </c>
-      <c r="J9" s="6">
-        <v>-0.3</v>
-      </c>
-      <c r="K9" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="N9" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="O9" s="6">
-        <v>1</v>
+      <c r="H9" s="14">
+        <f t="shared" ref="H9:O9" si="0">H8*$L$11</f>
+        <v>-140000</v>
+      </c>
+      <c r="I9" s="14">
+        <f t="shared" si="0"/>
+        <v>-70000</v>
+      </c>
+      <c r="J9" s="14">
+        <f t="shared" si="0"/>
+        <v>-42000</v>
+      </c>
+      <c r="K9" s="14">
+        <f t="shared" si="0"/>
+        <v>-14000</v>
+      </c>
+      <c r="L9" s="14">
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+      <c r="M9" s="14">
+        <f t="shared" si="0"/>
+        <v>42000</v>
+      </c>
+      <c r="N9" s="14">
+        <f t="shared" si="0"/>
+        <v>70000</v>
+      </c>
+      <c r="O9" s="14">
+        <f t="shared" si="0"/>
+        <v>140000</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="20">
-        <f>H9*$L$12</f>
-        <v>-140000</v>
-      </c>
-      <c r="I10" s="20">
-        <f t="shared" ref="I10:O10" si="0">I9*$L$12</f>
-        <v>-70000</v>
-      </c>
-      <c r="J10" s="20">
-        <f t="shared" si="0"/>
-        <v>-42000</v>
-      </c>
-      <c r="K10" s="20">
-        <f t="shared" si="0"/>
-        <v>-14000</v>
-      </c>
-      <c r="L10" s="20">
-        <f t="shared" si="0"/>
-        <v>14000</v>
-      </c>
-      <c r="M10" s="20">
-        <f t="shared" si="0"/>
-        <v>42000</v>
-      </c>
-      <c r="N10" s="20">
-        <f t="shared" si="0"/>
-        <v>70000</v>
-      </c>
-      <c r="O10" s="20">
-        <f t="shared" si="0"/>
-        <v>140000</v>
-      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
+      <c r="J11" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="16"/>
+      <c r="L11" s="17">
+        <v>140000</v>
+      </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-      <c r="J12" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="20">
-        <v>140000</v>
-      </c>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
       <c r="P12" s="18"/>
       <c r="Q12" s="18"/>
       <c r="R12" s="18"/>
@@ -1207,9 +889,14 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B13" s="15"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B14" s="15"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
@@ -1230,23 +917,311 @@
       <c r="H18" s="19"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8:A10">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+  <conditionalFormatting sqref="A4:A9">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:B7 A13:B16">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+  <conditionalFormatting sqref="A13:B16">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E476D5-D5F4-46B8-B8AE-896516844BE5}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:S17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="21">
+        <v>2.6557142857142869E-3</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0.62</v>
+      </c>
+      <c r="H5" s="22">
+        <v>0.65</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="21">
+        <v>-5.5166428571428582E-2</v>
+      </c>
+      <c r="G6" s="22">
+        <v>0.85</v>
+      </c>
+      <c r="H6" s="22">
+        <v>0.19</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="6">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="6">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="J8" s="6">
+        <v>-0.3</v>
+      </c>
+      <c r="K8" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="M8" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="O8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="20">
+        <f>H8*$L$11</f>
+        <v>-140000</v>
+      </c>
+      <c r="I9" s="20">
+        <f t="shared" ref="I9:O9" si="0">I8*$L$11</f>
+        <v>-70000</v>
+      </c>
+      <c r="J9" s="20">
+        <f t="shared" si="0"/>
+        <v>-42000</v>
+      </c>
+      <c r="K9" s="20">
+        <f t="shared" si="0"/>
+        <v>-14000</v>
+      </c>
+      <c r="L9" s="20">
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+      <c r="M9" s="20">
+        <f t="shared" si="0"/>
+        <v>42000</v>
+      </c>
+      <c r="N9" s="20">
+        <f t="shared" si="0"/>
+        <v>70000</v>
+      </c>
+      <c r="O9" s="20">
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="J11" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="16"/>
+      <c r="L11" s="20">
+        <v>140000</v>
+      </c>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B13" s="15"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="15"/>
+      <c r="H17" s="19"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A4">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:A9">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16:A17">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:B6 A12:B15">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1260,7 +1235,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="15" customWidth="1"/>
@@ -1316,7 +1291,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -1343,7 +1318,7 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="25">
         <f>2.8-2.79</f>
@@ -1356,7 +1331,7 @@
         <v>0.9</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -1369,7 +1344,7 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" s="25">
         <f>2.8-2.79</f>
@@ -1382,41 +1357,58 @@
         <v>0.54</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>22</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="E7" s="12"/>
       <c r="G7" s="12"/>
       <c r="H7" s="6">
-        <v>0.1</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>22</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F8" s="12"/>
       <c r="G8" s="12"/>
       <c r="H8" s="6">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="I8" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="J8" s="6">
+        <v>-0.3</v>
+      </c>
+      <c r="K8" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="M8" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="O8" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -1426,102 +1418,71 @@
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
-      <c r="H9" s="6">
-        <v>-1</v>
-      </c>
-      <c r="I9" s="6">
-        <v>-0.5</v>
-      </c>
-      <c r="J9" s="6">
-        <v>-0.3</v>
-      </c>
-      <c r="K9" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="N9" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="O9" s="6">
-        <v>1</v>
+      <c r="H9" s="20">
+        <f>H8*$L$11</f>
+        <v>-52000</v>
+      </c>
+      <c r="I9" s="20">
+        <f t="shared" ref="I9:O9" si="0">I8*$L$11</f>
+        <v>-26000</v>
+      </c>
+      <c r="J9" s="20">
+        <f t="shared" si="0"/>
+        <v>-15600</v>
+      </c>
+      <c r="K9" s="20">
+        <f t="shared" si="0"/>
+        <v>-5200</v>
+      </c>
+      <c r="L9" s="20">
+        <f t="shared" si="0"/>
+        <v>5200</v>
+      </c>
+      <c r="M9" s="20">
+        <f t="shared" si="0"/>
+        <v>15600</v>
+      </c>
+      <c r="N9" s="20">
+        <f t="shared" si="0"/>
+        <v>26000</v>
+      </c>
+      <c r="O9" s="20">
+        <f t="shared" si="0"/>
+        <v>52000</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="20">
-        <f>H9*$L$12</f>
-        <v>-52000</v>
-      </c>
-      <c r="I10" s="20">
-        <f t="shared" ref="I10:O10" si="0">I9*$L$12</f>
-        <v>-26000</v>
-      </c>
-      <c r="J10" s="20">
-        <f t="shared" si="0"/>
-        <v>-15600</v>
-      </c>
-      <c r="K10" s="20">
-        <f t="shared" si="0"/>
-        <v>-5200</v>
-      </c>
-      <c r="L10" s="20">
-        <f t="shared" si="0"/>
-        <v>5200</v>
-      </c>
-      <c r="M10" s="20">
-        <f t="shared" si="0"/>
-        <v>15600</v>
-      </c>
-      <c r="N10" s="20">
-        <f t="shared" si="0"/>
-        <v>26000</v>
-      </c>
-      <c r="O10" s="20">
-        <f t="shared" si="0"/>
-        <v>52000</v>
-      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
+      <c r="J11" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="16"/>
+      <c r="L11" s="26">
+        <v>52000</v>
+      </c>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-      <c r="J12" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="26">
-        <v>52000</v>
-      </c>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -1532,36 +1493,314 @@
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+      <c r="B15" s="15"/>
+      <c r="H15" s="19"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B16" s="15"/>
       <c r="H16" s="19"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="15"/>
-      <c r="H17" s="19"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A4:A8">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+  <conditionalFormatting sqref="A4:A9">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A16:A17">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+  <conditionalFormatting sqref="A15:A16">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13:B15">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+  <conditionalFormatting sqref="A12:B14">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9:A10">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B429D2-B3CE-459C-A93F-CE21A9784FDD}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:S16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="6.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="27">
+        <v>2E-3</v>
+      </c>
+      <c r="G5" s="27">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="H5" s="27">
+        <v>0.80200000000000005</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="27">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="G6" s="27">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="H6" s="27">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="6">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="6">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="J8" s="6">
+        <v>-0.3</v>
+      </c>
+      <c r="K8" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="M8" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="O8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="20">
+        <f>H8*$L$11</f>
+        <v>-52000</v>
+      </c>
+      <c r="I9" s="20">
+        <f t="shared" ref="I9:O9" si="0">I8*$L$11</f>
+        <v>-26000</v>
+      </c>
+      <c r="J9" s="20">
+        <f t="shared" si="0"/>
+        <v>-15600</v>
+      </c>
+      <c r="K9" s="20">
+        <f t="shared" si="0"/>
+        <v>-5200</v>
+      </c>
+      <c r="L9" s="20">
+        <f t="shared" si="0"/>
+        <v>5200</v>
+      </c>
+      <c r="M9" s="20">
+        <f t="shared" si="0"/>
+        <v>15600</v>
+      </c>
+      <c r="N9" s="20">
+        <f t="shared" si="0"/>
+        <v>26000</v>
+      </c>
+      <c r="O9" s="20">
+        <f t="shared" si="0"/>
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="J11" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="16"/>
+      <c r="L11" s="26">
+        <v>52000</v>
+      </c>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B15" s="15"/>
+      <c r="H15" s="19"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="H16" s="19"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A4:A9">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:A16">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B14">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
